--- a/artfynd/A 42503-2019 artfynd.xlsx
+++ b/artfynd/A 42503-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42503-2019 artfynd.xlsx
+++ b/artfynd/A 42503-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3239,127 +3239,6 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>114471964</v>
-      </c>
-      <c r="B24" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Skrubba, Srm</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>648133</v>
-      </c>
-      <c r="R24" t="n">
-        <v>6524954</v>
-      </c>
-      <c r="S24" t="n">
-        <v>25</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Trosa</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Trosa-Vagnhärad</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2024-01-31</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2024-01-31</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Lunglaven tycks trivas på sin ekstam. Angränsande område mot nordost är numera nästan trädfritt efter fällning främst av angripna och döda granar. Återstår att se om detta kommer att påverka beståndet av lunglav. Trots fler lämpliga träd i området kan jag inte finna arten på fler ställen.</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Göran Andersson</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Göran Andersson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
